--- a/data/ams_weekly_data/Nexlev/business_report_week26.xlsx
+++ b/data/ams_weekly_data/Nexlev/business_report_week26.xlsx
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>871</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1179</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -602,7 +602,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -614,7 +614,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>18297.46</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>10272</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -665,7 +665,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>13906</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -683,7 +683,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -695,7 +695,7 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>119211.01</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -746,7 +746,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -827,7 +827,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -908,7 +908,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>90686</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>111168</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1088,7 +1088,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1100,7 +1100,7 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>150008.49</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1151,7 +1151,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1169,7 +1169,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1181,7 +1181,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>4062.71</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1232,7 +1232,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1250,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1262,7 +1262,7 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>7145.77</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1313,7 +1313,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1331,7 +1331,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1343,7 +1343,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>677.12</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1412,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>846.61</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1668</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -1475,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2248</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1493,7 +1493,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1505,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>9658.469999999999</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1544,7 +1544,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1556,7 +1556,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1655,7 +1655,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -1667,7 +1667,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>760.17</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>852</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1718,7 +1718,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>982</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1736,7 +1736,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1748,7 +1748,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1522.89</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>314</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>378</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1829,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>8470.34</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1880,7 +1880,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1727.12</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -1949,7 +1949,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>545</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1961,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>845</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -1991,7 +1991,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>75244.07000000001</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>870</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -2042,7 +2042,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1166</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2060,7 +2060,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -2072,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>12098.32</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -2204,7 +2204,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -2234,7 +2234,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>7113.56</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -2285,7 +2285,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -2366,7 +2366,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2384,7 +2384,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -2396,7 +2396,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1523.73</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>284</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -2447,7 +2447,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>410</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -2465,7 +2465,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2477,7 +2477,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3811.02</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -2609,7 +2609,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -2690,7 +2690,7 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1047</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -2771,7 +2771,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -2801,7 +2801,7 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>7788.99</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>2588</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2852,7 +2852,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>3182</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>6639.83</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -2933,7 +2933,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -2951,7 +2951,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1439.83</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -3032,7 +3032,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -3044,7 +3044,7 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>5730.53</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3083,7 +3083,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>213</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -3095,7 +3095,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -3113,7 +3113,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -3125,7 +3125,7 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3388.14</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>17768</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -3176,7 +3176,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>24818</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -3194,7 +3194,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -3206,7 +3206,7 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>221815.28</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1038</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -3257,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1488</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -3275,7 +3275,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -3287,7 +3287,7 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>27630.51</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -3338,7 +3338,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -3368,7 +3368,7 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3388.14</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>582</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -3419,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>780</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -3437,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -3449,7 +3449,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>6353.39</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>16766</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -3500,7 +3500,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>20360</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -3518,7 +3518,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>115220.34</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3581,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -3662,7 +3662,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -3731,7 +3731,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -3743,7 +3743,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -3761,7 +3761,7 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -3773,7 +3773,7 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2371.19</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -3812,7 +3812,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>438</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -3824,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>614</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3842,7 +3842,7 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -3854,7 +3854,7 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>4548.31</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -3893,7 +3893,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>298</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -3974,7 +3974,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -3986,7 +3986,7 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -4067,7 +4067,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -4136,7 +4136,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -4148,7 +4148,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -4166,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -4178,7 +4178,7 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>3286.87</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -4229,7 +4229,7 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -4247,7 +4247,7 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -4259,7 +4259,7 @@
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>4319.49</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -4310,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -4328,7 +4328,7 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>1694.07</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -4391,7 +4391,7 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -4409,7 +4409,7 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -4421,7 +4421,7 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>1016.1</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -4472,7 +4472,7 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -4541,7 +4541,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -4553,7 +4553,7 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -4622,7 +4622,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -4634,7 +4634,7 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>418</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -4652,7 +4652,7 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -4664,7 +4664,7 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>1948.31</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -4715,7 +4715,7 @@
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -4733,7 +4733,7 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -4745,7 +4745,7 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>1524.58</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -4784,7 +4784,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -4796,7 +4796,7 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -4865,7 +4865,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>1778</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -4877,7 +4877,7 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>2428</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -4895,7 +4895,7 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>25413.56</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -4946,7 +4946,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>1379</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -4958,7 +4958,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>1859</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -4988,7 +4988,7 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>73678.82000000001</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
@@ -5027,7 +5027,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -5039,7 +5039,7 @@
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -5120,7 +5120,7 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -5189,7 +5189,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -5201,7 +5201,7 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>11896</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -5282,7 +5282,7 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>16320</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -5300,7 +5300,7 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -5312,7 +5312,7 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>177885.6</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
@@ -5351,7 +5351,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -5363,7 +5363,7 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>354</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -5381,7 +5381,7 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -5393,7 +5393,7 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>2540.68</v>
       </c>
       <c r="U61" t="n">
         <v>0</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>1998</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>2888</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -5462,7 +5462,7 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -5474,7 +5474,7 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>39938.14</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -5525,7 +5525,7 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -5543,7 +5543,7 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -5555,7 +5555,7 @@
         <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>1948.31</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -5594,7 +5594,7 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -5606,7 +5606,7 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>378</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -5687,7 +5687,7 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>490</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -5756,7 +5756,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -5768,7 +5768,7 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -5786,7 +5786,7 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -5798,7 +5798,7 @@
         <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>761.86</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
@@ -5837,7 +5837,7 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -5849,7 +5849,7 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -5867,7 +5867,7 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>1795.76</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -5918,7 +5918,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>376</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -5948,7 +5948,7 @@
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>
@@ -5960,7 +5960,7 @@
         <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>7116.95</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>9696</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -6011,7 +6011,7 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>13272</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -6029,7 +6029,7 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -6041,7 +6041,7 @@
         <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>190647.46</v>
       </c>
       <c r="U69" t="n">
         <v>0</v>
@@ -6080,7 +6080,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -6092,7 +6092,7 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -6110,7 +6110,7 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -6122,7 +6122,7 @@
         <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>9147.459999999999</v>
       </c>
       <c r="U70" t="n">
         <v>0</v>
@@ -6161,7 +6161,7 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -6173,7 +6173,7 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -6254,7 +6254,7 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -6323,7 +6323,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -6404,7 +6404,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -6416,7 +6416,7 @@
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -6497,7 +6497,7 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>323</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -6515,7 +6515,7 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -6527,7 +6527,7 @@
         <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>0</v>
+        <v>20335.59</v>
       </c>
       <c r="U75" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -6578,7 +6578,7 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -6647,7 +6647,7 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -6659,7 +6659,7 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -6677,7 +6677,7 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -6689,7 +6689,7 @@
         <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>253.39</v>
       </c>
       <c r="U77" t="n">
         <v>0</v>
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -6740,7 +6740,7 @@
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -6809,7 +6809,7 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -6821,7 +6821,7 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -6890,7 +6890,7 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -6902,7 +6902,7 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -6920,7 +6920,7 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -6932,7 +6932,7 @@
         <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>317.8</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -7001,7 +7001,7 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q81" t="n">
         <v>0</v>
@@ -7013,7 +7013,7 @@
         <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>148.31</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
@@ -7052,7 +7052,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>21118</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -7064,7 +7064,7 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>27932</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -7082,7 +7082,7 @@
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -7094,7 +7094,7 @@
         <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>0</v>
+        <v>261623.73</v>
       </c>
       <c r="U82" t="n">
         <v>0</v>
@@ -7133,7 +7133,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -7145,7 +7145,7 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>367</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -7163,7 +7163,7 @@
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -7175,7 +7175,7 @@
         <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>338.14</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
@@ -7214,7 +7214,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -7226,7 +7226,7 @@
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -7295,7 +7295,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -7307,7 +7307,7 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -7325,7 +7325,7 @@
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -7337,7 +7337,7 @@
         <v>0</v>
       </c>
       <c r="T85" t="n">
-        <v>0</v>
+        <v>2100.85</v>
       </c>
       <c r="U85" t="n">
         <v>0</v>
@@ -7376,7 +7376,7 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -7388,7 +7388,7 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -7418,7 +7418,7 @@
         <v>0</v>
       </c>
       <c r="T86" t="n">
-        <v>0</v>
+        <v>1354.24</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -7469,7 +7469,7 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -7550,7 +7550,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -7568,7 +7568,7 @@
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -7580,7 +7580,7 @@
         <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>677.12</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
@@ -7619,7 +7619,7 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -7631,7 +7631,7 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>423</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -7649,7 +7649,7 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>0</v>
+        <v>233.05</v>
       </c>
       <c r="U89" t="n">
         <v>0</v>
@@ -7700,7 +7700,7 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>602</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -7712,7 +7712,7 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>790</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -7730,7 +7730,7 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -7742,7 +7742,7 @@
         <v>0</v>
       </c>
       <c r="T90" t="n">
-        <v>0</v>
+        <v>67615.25</v>
       </c>
       <c r="U90" t="n">
         <v>0</v>
@@ -7781,7 +7781,7 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>3030</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -7793,7 +7793,7 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>4144</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -7811,7 +7811,7 @@
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -7823,7 +7823,7 @@
         <v>0</v>
       </c>
       <c r="T91" t="n">
-        <v>0</v>
+        <v>38120.34</v>
       </c>
       <c r="U91" t="n">
         <v>0</v>
@@ -7862,7 +7862,7 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -7874,7 +7874,7 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -7892,7 +7892,7 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
@@ -7904,7 +7904,7 @@
         <v>0</v>
       </c>
       <c r="T92" t="n">
-        <v>0</v>
+        <v>507.63</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
@@ -7943,7 +7943,7 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>892</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -7955,7 +7955,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>1171</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -7973,7 +7973,7 @@
         <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -7985,7 +7985,7 @@
         <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>0</v>
+        <v>6599.15</v>
       </c>
       <c r="U93" t="n">
         <v>0</v>
@@ -8024,7 +8024,7 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -8036,7 +8036,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
@@ -8066,7 +8066,7 @@
         <v>0</v>
       </c>
       <c r="T94" t="n">
-        <v>0</v>
+        <v>338.14</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
@@ -8105,7 +8105,7 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -8117,7 +8117,7 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -8135,7 +8135,7 @@
         <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -8147,7 +8147,7 @@
         <v>0</v>
       </c>
       <c r="T95" t="n">
-        <v>0</v>
+        <v>338.14</v>
       </c>
       <c r="U95" t="n">
         <v>0</v>
@@ -8186,7 +8186,7 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -8198,7 +8198,7 @@
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -8267,7 +8267,7 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>3328</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -8279,7 +8279,7 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>4864</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -8297,7 +8297,7 @@
         <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -8309,7 +8309,7 @@
         <v>0</v>
       </c>
       <c r="T97" t="n">
-        <v>0</v>
+        <v>172866.95</v>
       </c>
       <c r="U97" t="n">
         <v>0</v>
@@ -8348,7 +8348,7 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -8360,7 +8360,7 @@
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>712</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
@@ -8378,7 +8378,7 @@
         <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -8390,7 +8390,7 @@
         <v>0</v>
       </c>
       <c r="T98" t="n">
-        <v>0</v>
+        <v>19825.42</v>
       </c>
       <c r="U98" t="n">
         <v>0</v>
@@ -8429,7 +8429,7 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>248</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -8441,7 +8441,7 @@
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>343</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -8471,7 +8471,7 @@
         <v>0</v>
       </c>
       <c r="T99" t="n">
-        <v>0</v>
+        <v>5759.32</v>
       </c>
       <c r="U99" t="n">
         <v>0</v>
@@ -8510,7 +8510,7 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>1359</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -8522,7 +8522,7 @@
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
+        <v>1509</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -8540,7 +8540,7 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -8552,7 +8552,7 @@
         <v>0</v>
       </c>
       <c r="T100" t="n">
-        <v>0</v>
+        <v>48296.61</v>
       </c>
       <c r="U100" t="n">
         <v>0</v>
@@ -8591,7 +8591,7 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -8603,7 +8603,7 @@
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -8621,7 +8621,7 @@
         <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
         <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>0</v>
+        <v>9911.02</v>
       </c>
       <c r="U101" t="n">
         <v>0</v>
@@ -8672,7 +8672,7 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -8684,7 +8684,7 @@
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="K102" t="n">
         <v>0</v>
@@ -8753,7 +8753,7 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>0</v>
+        <v>711</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -8765,7 +8765,7 @@
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
+        <v>984</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
@@ -8783,7 +8783,7 @@
         <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q103" t="n">
         <v>0</v>
@@ -8795,7 +8795,7 @@
         <v>0</v>
       </c>
       <c r="T103" t="n">
-        <v>0</v>
+        <v>71062.72</v>
       </c>
       <c r="U103" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -8846,7 +8846,7 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>436</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
@@ -8864,7 +8864,7 @@
         <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
@@ -8876,7 +8876,7 @@
         <v>0</v>
       </c>
       <c r="T104" t="n">
-        <v>0</v>
+        <v>29320.34</v>
       </c>
       <c r="U104" t="n">
         <v>0</v>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -8927,7 +8927,7 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -8945,7 +8945,7 @@
         <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
@@ -8957,7 +8957,7 @@
         <v>0</v>
       </c>
       <c r="T105" t="n">
-        <v>0</v>
+        <v>1686.44</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
